--- a/xls/square_20_tri3_13.xlsx
+++ b/xls/square_20_tri3_13.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>196</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>441</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>144</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11">
+        <v>726</v>
+      </c>
+      <c r="I11">
+        <v>5.242928277300394</v>
+      </c>
+      <c r="J11">
+        <v>1.2567223655365702</v>
+      </c>
+      <c r="K11">
+        <v>1.906424582021893</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>196</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12">
+        <v>441</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12">
+        <v>169</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12">
+        <v>864</v>
+      </c>
+      <c r="I12">
+        <v>3.852122070688315</v>
+      </c>
+      <c r="J12">
+        <v>0.30394448129724444</v>
+      </c>
+      <c r="K12">
+        <v>1.17586494618937</v>
+      </c>
+    </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>11</v>
